--- a/benchmarks_tests/FINAL_Benchmarks_for_paper/PySCF_scaling_behavior_CAO_old.xlsx
+++ b/benchmarks_tests/FINAL_Benchmarks_for_paper/PySCF_scaling_behavior_CAO_old.xlsx
@@ -1,19 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10810"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10125"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/manas/Documents/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/manas/Documents/PyFock__Benchmarks_Paper_IJQC/FINAL_Benchmarks_for_paper/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C1B5B414-C7FC-674C-B4BB-EE580800FC2B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{36799D2B-A6A9-694E-9256-DA0161B94095}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1360" yWindow="760" windowWidth="28040" windowHeight="16960" xr2:uid="{580CF0B2-FD39-1547-AD8E-82680C382266}"/>
+    <workbookView xWindow="1360" yWindow="760" windowWidth="28040" windowHeight="16860" activeTab="1" xr2:uid="{580CF0B2-FD39-1547-AD8E-82680C382266}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="def2-TZVP" sheetId="2" r:id="rId1"/>
+    <sheet name="def2-SVP" sheetId="1" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -36,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="11">
   <si>
     <t>Scaling behavior</t>
   </si>
@@ -75,6 +76,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.000"/>
+  </numFmts>
   <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
@@ -117,13 +121,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -226,7 +231,7 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>Sheet1!$B$19</c:f>
+              <c:f>'def2-TZVP'!$B$19</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -261,7 +266,7 @@
           </c:marker>
           <c:xVal>
             <c:numRef>
-              <c:f>Sheet1!$A$20:$A$28</c:f>
+              <c:f>'def2-TZVP'!$A$20:$A$28</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="9"/>
@@ -297,13 +302,1077 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>Sheet1!$B$20:$B$28</c:f>
+              <c:f>'def2-TZVP'!$B$20:$B$28</c:f>
+              <c:numCache>
+                <c:formatCode>0.000</c:formatCode>
+                <c:ptCount val="9"/>
+                <c:pt idx="0">
+                  <c:v>5.5805761134251876E-2</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.64725175760686393</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>2.9523591290538498</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>11.847672193843286</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>30.462757464232144</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>62.136707197475644</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>173.97918536944749</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>302.25592349022605</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>590.43874584103435</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="1"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-93A2-8548-9C7F-ACE393F71ADE}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="2146806720"/>
+        <c:axId val="955075920"/>
+      </c:scatterChart>
+      <c:valAx>
+        <c:axId val="2146806720"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-GB"/>
+                  <a:t>No. of Water Molecules</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="955075920"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="955075920"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-GB"/>
+                  <a:t>Wall Time  per Iteration (s)</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="0.000" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="2146806720"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-GB"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-GB" sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:sysClr val="windowText" lastClr="000000">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:sysClr>
+                </a:solidFill>
+              </a:rPr>
+              <a:t>Scaling behavior of KS-DFT Calculations using PySCF</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:scatterChart>
+        <c:scatterStyle val="smoothMarker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'def2-TZVP'!$H$19</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Total Time Taken (s) / iter</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>'def2-TZVP'!$G$20:$G$28</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="9"/>
                 <c:pt idx="0">
-                  <c:v>5.9873508249999999E-2</c:v>
-                </c:pt>
+                  <c:v>48</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>240</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>480</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>960</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>1536</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>2256</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>3648</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>4800</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>6672</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>'def2-TZVP'!$H$20:$H$28</c:f>
+              <c:numCache>
+                <c:formatCode>0.000</c:formatCode>
+                <c:ptCount val="9"/>
+                <c:pt idx="0">
+                  <c:v>5.5805761134251876E-2</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.64725175760686393</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>2.9523591290538498</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>11.847672193843286</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>30.462757464232144</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>62.136707197475644</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>173.97918536944749</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>302.25592349022605</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>590.43874584103435</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="1"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-D6FB-A34F-B03B-B554DEA2A24D}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="343240127"/>
+        <c:axId val="343241855"/>
+      </c:scatterChart>
+      <c:valAx>
+        <c:axId val="343240127"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-GB"/>
+                  <a:t>No. of Basis Functions (</a:t>
+                </a:r>
+                <a:r>
+                  <a:rPr lang="en-GB" i="1"/>
+                  <a:t>Nbf</a:t>
+                </a:r>
+                <a:r>
+                  <a:rPr lang="en-GB"/>
+                  <a:t>)</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="343241855"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="343241855"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-GB" sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:sysClr val="windowText" lastClr="000000">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:sysClr>
+                    </a:solidFill>
+                  </a:rPr>
+                  <a:t>Wall Time per Iteration (s)</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="0.000" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="343240127"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-GB"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-GB"/>
+              <a:t>Scaling behavior of KS-DFT</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="en-GB" baseline="0"/>
+              <a:t> Calculations using PySCF</a:t>
+            </a:r>
+            <a:endParaRPr lang="en-GB"/>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-GB"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:scatterChart>
+        <c:scatterStyle val="smoothMarker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'def2-SVP'!$B$19</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Total Time Taken (s) / iter</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>'def2-SVP'!$A$20:$A$28</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="9"/>
+                <c:pt idx="0">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>20</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>32</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>47</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>76</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>100</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>139</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>'def2-SVP'!$B$20:$B$28</c:f>
+              <c:numCache>
+                <c:formatCode>0.000</c:formatCode>
+                <c:ptCount val="9"/>
                 <c:pt idx="1">
                   <c:v>0.35198503380000001</c:v>
                 </c:pt>
@@ -542,7 +1611,7 @@
             </a:p>
           </c:txPr>
         </c:title>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:numFmt formatCode="0.000" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
@@ -666,7 +1735,7 @@
 </c:chartSpace>
 </file>
 
-<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
   <c:lang val="en-GB"/>
@@ -753,7 +1822,7 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>Sheet1!$H$19</c:f>
+              <c:f>'def2-SVP'!$H$19</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -788,7 +1857,7 @@
           </c:marker>
           <c:xVal>
             <c:numRef>
-              <c:f>Sheet1!$G$20:$G$28</c:f>
+              <c:f>'def2-SVP'!$G$20:$G$28</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="9"/>
@@ -824,13 +1893,10 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>Sheet1!$H$20:$H$28</c:f>
+              <c:f>'def2-SVP'!$H$20:$H$28</c:f>
               <c:numCache>
-                <c:formatCode>General</c:formatCode>
+                <c:formatCode>0.000</c:formatCode>
                 <c:ptCount val="9"/>
-                <c:pt idx="0">
-                  <c:v>5.9873508249999999E-2</c:v>
-                </c:pt>
                 <c:pt idx="1">
                   <c:v>0.35198503380000001</c:v>
                 </c:pt>
@@ -1084,7 +2150,7 @@
             </a:p>
           </c:txPr>
         </c:title>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:numFmt formatCode="0.000" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
@@ -1288,6 +2354,86 @@
 </cs:colorStyle>
 </file>
 
+<file path=xl/charts/colors3.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors4.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
 <file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
   <cs:axisTitle>
@@ -2320,7 +3466,1120 @@
 </cs:chartStyle>
 </file>
 
+<file path=xl/charts/style3.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style4.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>57150</xdr:colOff>
+      <xdr:row>28</xdr:row>
+      <xdr:rowOff>82550</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>228600</xdr:colOff>
+      <xdr:row>45</xdr:row>
+      <xdr:rowOff>190500</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="Chart 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4BB1A032-68FD-DE4E-8154-AC5775AF2F98}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>209550</xdr:colOff>
+      <xdr:row>28</xdr:row>
+      <xdr:rowOff>190500</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>812800</xdr:colOff>
+      <xdr:row>46</xdr:row>
+      <xdr:rowOff>120650</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="3" name="Chart 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{261FA807-C249-8742-A772-42C4A13B57B8}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
@@ -2713,6 +4972,440 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6E69A6A4-0832-B24C-8394-DC1CA58CAEAB}">
+  <dimension ref="A1:J28"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="20" customWidth="1"/>
+    <col min="2" max="2" width="22.1640625" customWidth="1"/>
+    <col min="3" max="3" width="17.83203125" customWidth="1"/>
+    <col min="5" max="5" width="23.83203125" customWidth="1"/>
+    <col min="7" max="7" width="23.6640625" customWidth="1"/>
+    <col min="8" max="8" width="14.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A2" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A3" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A4" s="2" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A6" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="H6" s="2"/>
+      <c r="I6" s="2"/>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A7">
+        <v>1</v>
+      </c>
+      <c r="B7">
+        <v>48</v>
+      </c>
+      <c r="C7" s="1">
+        <v>0.44644608907401501</v>
+      </c>
+      <c r="D7" s="3">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="E7" s="1">
+        <f>C7-D7</f>
+        <v>0.376446089074015</v>
+      </c>
+      <c r="F7" s="1">
+        <v>8</v>
+      </c>
+      <c r="G7">
+        <f t="shared" ref="G7:G15" si="0">C7/F7</f>
+        <v>5.5805761134251876E-2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A8">
+        <v>5</v>
+      </c>
+      <c r="B8">
+        <v>240</v>
+      </c>
+      <c r="C8" s="1">
+        <v>6.4725175760686398</v>
+      </c>
+      <c r="D8" s="3">
+        <v>0.3</v>
+      </c>
+      <c r="E8" s="1">
+        <f t="shared" ref="E8:E15" si="1">C8-D8</f>
+        <v>6.1725175760686399</v>
+      </c>
+      <c r="F8" s="1">
+        <v>10</v>
+      </c>
+      <c r="G8">
+        <f t="shared" si="0"/>
+        <v>0.64725175760686393</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A9">
+        <v>10</v>
+      </c>
+      <c r="B9">
+        <v>480</v>
+      </c>
+      <c r="C9" s="1">
+        <v>35.428309548646197</v>
+      </c>
+      <c r="D9" s="3">
+        <v>1.45</v>
+      </c>
+      <c r="E9" s="1">
+        <f t="shared" si="1"/>
+        <v>33.978309548646195</v>
+      </c>
+      <c r="F9" s="1">
+        <v>12</v>
+      </c>
+      <c r="G9">
+        <f t="shared" si="0"/>
+        <v>2.9523591290538498</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A10">
+        <v>20</v>
+      </c>
+      <c r="B10">
+        <v>960</v>
+      </c>
+      <c r="C10" s="1">
+        <v>165.86741071380601</v>
+      </c>
+      <c r="D10" s="3">
+        <v>5.92</v>
+      </c>
+      <c r="E10" s="1">
+        <f t="shared" si="1"/>
+        <v>159.94741071380602</v>
+      </c>
+      <c r="F10" s="1">
+        <v>14</v>
+      </c>
+      <c r="G10">
+        <f t="shared" si="0"/>
+        <v>11.847672193843286</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A11">
+        <v>32</v>
+      </c>
+      <c r="B11">
+        <v>1536</v>
+      </c>
+      <c r="C11" s="1">
+        <v>426.47860449925003</v>
+      </c>
+      <c r="D11" s="3">
+        <v>15.61</v>
+      </c>
+      <c r="E11" s="1">
+        <f t="shared" si="1"/>
+        <v>410.86860449925001</v>
+      </c>
+      <c r="F11" s="1">
+        <v>14</v>
+      </c>
+      <c r="G11">
+        <f t="shared" si="0"/>
+        <v>30.462757464232144</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A12">
+        <v>47</v>
+      </c>
+      <c r="B12">
+        <v>2256</v>
+      </c>
+      <c r="C12" s="1">
+        <v>869.91390076465905</v>
+      </c>
+      <c r="D12" s="3">
+        <v>36.72</v>
+      </c>
+      <c r="E12" s="1">
+        <f>C12-D12</f>
+        <v>833.19390076465902</v>
+      </c>
+      <c r="F12" s="1">
+        <v>14</v>
+      </c>
+      <c r="G12">
+        <f t="shared" si="0"/>
+        <v>62.136707197475644</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A13">
+        <v>76</v>
+      </c>
+      <c r="B13">
+        <v>3648</v>
+      </c>
+      <c r="C13" s="1">
+        <v>2783.6669659111599</v>
+      </c>
+      <c r="D13" s="3">
+        <v>109.71</v>
+      </c>
+      <c r="E13" s="1">
+        <f t="shared" si="1"/>
+        <v>2673.9569659111598</v>
+      </c>
+      <c r="F13" s="1">
+        <v>16</v>
+      </c>
+      <c r="G13">
+        <f t="shared" si="0"/>
+        <v>173.97918536944749</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A14">
+        <v>100</v>
+      </c>
+      <c r="B14">
+        <v>4800</v>
+      </c>
+      <c r="C14" s="1">
+        <v>4533.8388523533904</v>
+      </c>
+      <c r="D14" s="3">
+        <v>206.88</v>
+      </c>
+      <c r="E14" s="1">
+        <f t="shared" si="1"/>
+        <v>4326.9588523533903</v>
+      </c>
+      <c r="F14" s="1">
+        <v>15</v>
+      </c>
+      <c r="G14">
+        <f t="shared" si="0"/>
+        <v>302.25592349022605</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A15">
+        <v>139</v>
+      </c>
+      <c r="B15">
+        <v>6672</v>
+      </c>
+      <c r="C15" s="1">
+        <v>9447.0199334565496</v>
+      </c>
+      <c r="D15" s="3">
+        <v>510.37</v>
+      </c>
+      <c r="E15" s="1">
+        <f t="shared" si="1"/>
+        <v>8936.6499334565488</v>
+      </c>
+      <c r="F15" s="1">
+        <v>16</v>
+      </c>
+      <c r="G15">
+        <f t="shared" si="0"/>
+        <v>590.43874584103435</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A19" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C19" s="2"/>
+      <c r="D19" s="2"/>
+      <c r="G19" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="H19" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="I19" s="2"/>
+      <c r="J19" s="2"/>
+    </row>
+    <row r="20" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A20">
+        <v>1</v>
+      </c>
+      <c r="B20" s="4">
+        <v>5.5805761134251876E-2</v>
+      </c>
+      <c r="G20">
+        <v>48</v>
+      </c>
+      <c r="H20" s="4">
+        <v>5.5805761134251876E-2</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A21">
+        <v>5</v>
+      </c>
+      <c r="B21" s="4">
+        <v>0.64725175760686393</v>
+      </c>
+      <c r="G21">
+        <v>240</v>
+      </c>
+      <c r="H21" s="4">
+        <v>0.64725175760686393</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A22">
+        <v>10</v>
+      </c>
+      <c r="B22" s="4">
+        <v>2.9523591290538498</v>
+      </c>
+      <c r="G22">
+        <v>480</v>
+      </c>
+      <c r="H22" s="4">
+        <v>2.9523591290538498</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A23">
+        <v>20</v>
+      </c>
+      <c r="B23" s="4">
+        <v>11.847672193843286</v>
+      </c>
+      <c r="G23">
+        <v>960</v>
+      </c>
+      <c r="H23" s="4">
+        <v>11.847672193843286</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A24">
+        <v>32</v>
+      </c>
+      <c r="B24" s="4">
+        <v>30.462757464232144</v>
+      </c>
+      <c r="G24">
+        <v>1536</v>
+      </c>
+      <c r="H24" s="4">
+        <v>30.462757464232144</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A25">
+        <v>47</v>
+      </c>
+      <c r="B25" s="4">
+        <v>62.136707197475644</v>
+      </c>
+      <c r="G25">
+        <v>2256</v>
+      </c>
+      <c r="H25" s="4">
+        <v>62.136707197475644</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A26">
+        <v>76</v>
+      </c>
+      <c r="B26" s="4">
+        <v>173.97918536944749</v>
+      </c>
+      <c r="G26">
+        <v>3648</v>
+      </c>
+      <c r="H26" s="4">
+        <v>173.97918536944749</v>
+      </c>
+    </row>
+    <row r="27" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A27">
+        <v>100</v>
+      </c>
+      <c r="B27" s="4">
+        <v>302.25592349022605</v>
+      </c>
+      <c r="G27">
+        <v>4800</v>
+      </c>
+      <c r="H27" s="4">
+        <v>302.25592349022605</v>
+      </c>
+    </row>
+    <row r="28" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A28">
+        <v>139</v>
+      </c>
+      <c r="B28" s="4">
+        <v>590.43874584103435</v>
+      </c>
+      <c r="G28">
+        <v>6672</v>
+      </c>
+      <c r="H28" s="4">
+        <v>590.43874584103435</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B781A2DA-171B-7249-99BA-E5D7419364B8}">
   <dimension ref="A1:J28"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
@@ -2791,7 +5484,7 @@
         <v>8</v>
       </c>
       <c r="G7">
-        <f>C7/F7</f>
+        <f t="shared" ref="G7:G15" si="0">C7/F7</f>
         <v>5.9873508249999999E-2</v>
       </c>
     </row>
@@ -2809,14 +5502,14 @@
         <v>0.27</v>
       </c>
       <c r="E8" s="1">
-        <f t="shared" ref="E8:E15" si="0">C8-D8</f>
+        <f t="shared" ref="E8:E15" si="1">C8-D8</f>
         <v>3.2498503379999999</v>
       </c>
       <c r="F8" s="1">
         <v>10</v>
       </c>
       <c r="G8">
-        <f>C8/F8</f>
+        <f t="shared" si="0"/>
         <v>0.35198503380000001</v>
       </c>
     </row>
@@ -2834,14 +5527,14 @@
         <v>0.82</v>
       </c>
       <c r="E9" s="1">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>17.722971040000001</v>
       </c>
       <c r="F9" s="1">
         <v>12</v>
       </c>
       <c r="G9">
-        <f>C9/F9</f>
+        <f t="shared" si="0"/>
         <v>1.5452475866666668</v>
       </c>
     </row>
@@ -2859,14 +5552,14 @@
         <v>3.77</v>
       </c>
       <c r="E10" s="1">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>75.400255979999997</v>
       </c>
       <c r="F10" s="1">
         <v>14</v>
       </c>
       <c r="G10">
-        <f>C10/F10</f>
+        <f t="shared" si="0"/>
         <v>5.6550182842857142</v>
       </c>
     </row>
@@ -2884,14 +5577,14 @@
         <v>10.77</v>
       </c>
       <c r="E11" s="1">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>193.03665289999998</v>
       </c>
       <c r="F11" s="1">
         <v>15</v>
       </c>
       <c r="G11">
-        <f>C11/F11</f>
+        <f t="shared" si="0"/>
         <v>13.587110193333332</v>
       </c>
     </row>
@@ -2916,7 +5609,7 @@
         <v>15</v>
       </c>
       <c r="G12">
-        <f>C12/F12</f>
+        <f t="shared" si="0"/>
         <v>28.773918373333334</v>
       </c>
     </row>
@@ -2934,14 +5627,14 @@
         <v>88.31</v>
       </c>
       <c r="E13" s="1">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>994.93603099999996</v>
       </c>
       <c r="F13" s="1">
         <v>16</v>
       </c>
       <c r="G13">
-        <f>C13/F13</f>
+        <f t="shared" si="0"/>
         <v>67.702876937499994</v>
       </c>
     </row>
@@ -2959,14 +5652,14 @@
         <v>173.2</v>
       </c>
       <c r="E14" s="1">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>2165.8883770000002</v>
       </c>
       <c r="F14" s="1">
         <v>18</v>
       </c>
       <c r="G14">
-        <f>C14/F14</f>
+        <f t="shared" si="0"/>
         <v>129.94935427777779</v>
       </c>
     </row>
@@ -2984,14 +5677,14 @@
         <v>477.48</v>
       </c>
       <c r="E15" s="1">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>3723.6654809999995</v>
       </c>
       <c r="F15" s="1">
         <v>16</v>
       </c>
       <c r="G15">
-        <f>C15/F15</f>
+        <f t="shared" si="0"/>
         <v>262.57159256249997</v>
       </c>
     </row>
@@ -3017,27 +5710,23 @@
       <c r="A20">
         <v>1</v>
       </c>
-      <c r="B20">
-        <v>5.9873508249999999E-2</v>
-      </c>
+      <c r="B20" s="4"/>
       <c r="G20">
         <v>25</v>
       </c>
-      <c r="H20">
-        <v>5.9873508249999999E-2</v>
-      </c>
+      <c r="H20" s="4"/>
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A21">
         <v>5</v>
       </c>
-      <c r="B21">
+      <c r="B21" s="4">
         <v>0.35198503380000001</v>
       </c>
       <c r="G21">
         <v>125</v>
       </c>
-      <c r="H21">
+      <c r="H21" s="4">
         <v>0.35198503380000001</v>
       </c>
     </row>
@@ -3045,13 +5734,13 @@
       <c r="A22">
         <v>10</v>
       </c>
-      <c r="B22">
+      <c r="B22" s="4">
         <v>1.5452475866666668</v>
       </c>
       <c r="G22">
         <v>250</v>
       </c>
-      <c r="H22">
+      <c r="H22" s="4">
         <v>1.5452475866666668</v>
       </c>
     </row>
@@ -3059,13 +5748,13 @@
       <c r="A23">
         <v>20</v>
       </c>
-      <c r="B23">
+      <c r="B23" s="4">
         <v>5.6550182842857142</v>
       </c>
       <c r="G23">
         <v>500</v>
       </c>
-      <c r="H23">
+      <c r="H23" s="4">
         <v>5.6550182842857142</v>
       </c>
     </row>
@@ -3073,13 +5762,13 @@
       <c r="A24">
         <v>32</v>
       </c>
-      <c r="B24">
+      <c r="B24" s="4">
         <v>13.587110193333332</v>
       </c>
       <c r="G24">
         <v>800</v>
       </c>
-      <c r="H24">
+      <c r="H24" s="4">
         <v>13.587110193333332</v>
       </c>
     </row>
@@ -3087,13 +5776,13 @@
       <c r="A25">
         <v>47</v>
       </c>
-      <c r="B25">
+      <c r="B25" s="4">
         <v>28.773918373333334</v>
       </c>
       <c r="G25">
         <v>1175</v>
       </c>
-      <c r="H25">
+      <c r="H25" s="4">
         <v>28.773918373333334</v>
       </c>
     </row>
@@ -3101,13 +5790,13 @@
       <c r="A26">
         <v>76</v>
       </c>
-      <c r="B26">
+      <c r="B26" s="4">
         <v>67.702876937499994</v>
       </c>
       <c r="G26">
         <v>1900</v>
       </c>
-      <c r="H26">
+      <c r="H26" s="4">
         <v>67.702876937499994</v>
       </c>
     </row>
@@ -3115,13 +5804,13 @@
       <c r="A27">
         <v>100</v>
       </c>
-      <c r="B27">
+      <c r="B27" s="4">
         <v>129.94935427777779</v>
       </c>
       <c r="G27">
         <v>2500</v>
       </c>
-      <c r="H27">
+      <c r="H27" s="4">
         <v>129.94935427777779</v>
       </c>
     </row>
@@ -3129,13 +5818,13 @@
       <c r="A28">
         <v>139</v>
       </c>
-      <c r="B28">
+      <c r="B28" s="4">
         <v>262.57159256249997</v>
       </c>
       <c r="G28">
         <v>3475</v>
       </c>
-      <c r="H28">
+      <c r="H28" s="4">
         <v>262.57159256249997</v>
       </c>
     </row>
